--- a/test-data/Officers_Template.xlsx
+++ b/test-data/Officers_Template.xlsx
@@ -398,21 +398,24 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M3"/>
+  <dimension ref="A1:P3"/>
   <cols>
     <col min="1" max="1" width="12.83203125" customWidth="1"/>
     <col min="2" max="2" width="24.83203125" customWidth="1"/>
     <col min="3" max="3" width="22.83203125" customWidth="1"/>
-    <col min="4" max="4" width="28.83203125" customWidth="1"/>
-    <col min="5" max="5" width="26.83203125" customWidth="1"/>
-    <col min="6" max="6" width="13.83203125" customWidth="1"/>
-    <col min="7" max="7" width="24.83203125" customWidth="1"/>
-    <col min="8" max="8" width="16.83203125" customWidth="1"/>
-    <col min="9" max="9" width="16.83203125" customWidth="1"/>
+    <col min="4" max="4" width="12.83203125" customWidth="1"/>
+    <col min="5" max="5" width="28.83203125" customWidth="1"/>
+    <col min="6" max="6" width="26.83203125" customWidth="1"/>
+    <col min="7" max="7" width="13.83203125" customWidth="1"/>
+    <col min="8" max="8" width="24.83203125" customWidth="1"/>
+    <col min="9" max="9" width="12.83203125" customWidth="1"/>
     <col min="10" max="10" width="16.83203125" customWidth="1"/>
-    <col min="11" max="11" width="14.83203125" customWidth="1"/>
-    <col min="12" max="12" width="14.83203125" customWidth="1"/>
-    <col min="13" max="13" width="13.83203125" customWidth="1"/>
+    <col min="11" max="11" width="12.83203125" customWidth="1"/>
+    <col min="12" max="12" width="16.83203125" customWidth="1"/>
+    <col min="13" max="13" width="16.83203125" customWidth="1"/>
+    <col min="14" max="14" width="14.83203125" customWidth="1"/>
+    <col min="15" max="15" width="14.83203125" customWidth="1"/>
+    <col min="16" max="16" width="13.83203125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -426,33 +429,42 @@
         <v>Designation</v>
       </c>
       <c r="D1" t="str">
+        <v>Office Code</v>
+      </c>
+      <c r="E1" t="str">
         <v>Office Name</v>
       </c>
-      <c r="E1" t="str">
+      <c r="F1" t="str">
         <v>Office Address</v>
       </c>
-      <c r="F1" t="str">
+      <c r="G1" t="str">
         <v>Mobile</v>
       </c>
-      <c r="G1" t="str">
+      <c r="H1" t="str">
         <v>Duty</v>
       </c>
-      <c r="H1" t="str">
+      <c r="I1" t="str">
+        <v>Home Block Code</v>
+      </c>
+      <c r="J1" t="str">
         <v>Home Block</v>
       </c>
-      <c r="I1" t="str">
+      <c r="K1" t="str">
+        <v>Posting Block Code</v>
+      </c>
+      <c r="L1" t="str">
         <v>Posting Block</v>
       </c>
-      <c r="J1" t="str">
+      <c r="M1" t="str">
         <v>Account No</v>
       </c>
-      <c r="K1" t="str">
+      <c r="N1" t="str">
         <v>Bank</v>
       </c>
-      <c r="L1" t="str">
+      <c r="O1" t="str">
         <v>Branch</v>
       </c>
-      <c r="M1" t="str">
+      <c r="P1" t="str">
         <v>IFSC</v>
       </c>
     </row>
@@ -467,33 +479,42 @@
         <v>Headmaster</v>
       </c>
       <c r="D2" t="str">
+        <v>10231</v>
+      </c>
+      <c r="E2" t="str">
         <v>Middle School Piprahi</v>
       </c>
-      <c r="E2" t="str">
+      <c r="F2" t="str">
         <v>Piprahi</v>
       </c>
-      <c r="F2" t="str">
+      <c r="G2" t="str">
         <v>9000000001</v>
       </c>
-      <c r="G2" t="str">
+      <c r="H2" t="str">
         <v>PRESIDING OFFICER</v>
       </c>
-      <c r="H2" t="str">
+      <c r="I2" t="str">
+        <v>0101</v>
+      </c>
+      <c r="J2" t="str">
         <v>Sheohar</v>
       </c>
-      <c r="I2" t="str">
+      <c r="K2" t="str">
+        <v>0102</v>
+      </c>
+      <c r="L2" t="str">
         <v>Piprahi</v>
       </c>
-      <c r="J2" t="str">
+      <c r="M2" t="str">
         <v>1234567890</v>
       </c>
-      <c r="K2" t="str">
+      <c r="N2" t="str">
         <v>SBI</v>
       </c>
-      <c r="L2" t="str">
+      <c r="O2" t="str">
         <v>Sheohar</v>
       </c>
-      <c r="M2" t="str">
+      <c r="P2" t="str">
         <v>SBIN0000001</v>
       </c>
     </row>
@@ -508,39 +529,48 @@
         <v>Teacher</v>
       </c>
       <c r="D3" t="str">
+        <v>10458</v>
+      </c>
+      <c r="E3" t="str">
         <v>High School Tariyani</v>
       </c>
-      <c r="E3" t="str">
+      <c r="F3" t="str">
         <v>Tariyani</v>
       </c>
-      <c r="F3" t="str">
+      <c r="G3" t="str">
         <v>9000000002</v>
       </c>
-      <c r="G3" t="str">
+      <c r="H3" t="str">
         <v>POLLING OFFICER-1</v>
       </c>
-      <c r="H3" t="str">
+      <c r="I3" t="str">
+        <v>0105</v>
+      </c>
+      <c r="J3" t="str">
         <v>Tariyani</v>
       </c>
-      <c r="I3" t="str">
+      <c r="K3" t="str">
+        <v>0105</v>
+      </c>
+      <c r="L3" t="str">
         <v>Tariyani</v>
-      </c>
-      <c r="J3" t="str">
-        <v/>
-      </c>
-      <c r="K3" t="str">
-        <v/>
-      </c>
-      <c r="L3" t="str">
-        <v/>
       </c>
       <c r="M3" t="str">
         <v/>
       </c>
+      <c r="N3" t="str">
+        <v/>
+      </c>
+      <c r="O3" t="str">
+        <v/>
+      </c>
+      <c r="P3" t="str">
+        <v/>
+      </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:M3"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:P3"/>
   </ignoredErrors>
 </worksheet>
 </file>
@@ -564,12 +594,12 @@
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>Officers — Home Block and Posting Block are used for exclusion: nobody is tagged to a booth in his/her home or posting block.</v>
+        <v>Officers — Home Block (Code) and Posting Block (Code) are used for exclusion: nobody is tagged to a booth in his/her home or posting block. When both officer and booth have a block code (e.g. census code), the code decides.</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>Officers — Office Name is used for the rule that the 4 members of a party must be from different offices.</v>
+        <v>Officers — Office Code (or Office Name if no code) is used for the rule that the 4 members of a party must be from different offices. Codes protect against spelling mistakes in names.</v>
       </c>
     </row>
     <row r="5">

--- a/test-data/Officers_Template.xlsx
+++ b/test-data/Officers_Template.xlsx
@@ -398,7 +398,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:P3"/>
+  <dimension ref="A1:P4"/>
   <cols>
     <col min="1" max="1" width="12.83203125" customWidth="1"/>
     <col min="2" max="2" width="24.83203125" customWidth="1"/>
@@ -568,53 +568,148 @@
         <v/>
       </c>
     </row>
+    <row r="4">
+      <c r="A4" t="str">
+        <v/>
+      </c>
+      <c r="B4" t="str">
+        <v>MANOJ SINGH</v>
+      </c>
+      <c r="C4" t="str">
+        <v>Branch Manager</v>
+      </c>
+      <c r="D4" t="str">
+        <v>20017</v>
+      </c>
+      <c r="E4" t="str">
+        <v>State Bank of India, Sheohar</v>
+      </c>
+      <c r="F4" t="str">
+        <v>Sheohar</v>
+      </c>
+      <c r="G4" t="str">
+        <v>9000000003</v>
+      </c>
+      <c r="H4" t="str">
+        <v>MICRO OBSERVER</v>
+      </c>
+      <c r="I4" t="str">
+        <v>999999</v>
+      </c>
+      <c r="J4" t="str">
+        <v>Others</v>
+      </c>
+      <c r="K4" t="str">
+        <v>0101</v>
+      </c>
+      <c r="L4" t="str">
+        <v>Sheohar</v>
+      </c>
+      <c r="M4" t="str">
+        <v/>
+      </c>
+      <c r="N4" t="str">
+        <v/>
+      </c>
+      <c r="O4" t="str">
+        <v/>
+      </c>
+      <c r="P4" t="str">
+        <v/>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:P3"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:P4"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:A6"/>
+  <dimension ref="A1:A15"/>
   <cols>
     <col min="1" max="1" width="120.83203125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
-        <v>Officers — Duty must be one of: PRESIDING OFFICER, POLLING OFFICER-1, POLLING OFFICER-2, POLLING OFFICER-3, PATROLLING MAGISTRATE, MICRO OBSERVER</v>
+        <v>OFFICERS — one row per officer. Delete the three example rows before use.</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v xml:space="preserve">          (short forms PrO, P1, P2, P3, PCCP, MO are also accepted).</v>
+        <v/>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>Officers — Home Block (Code) and Posting Block (Code) are used for exclusion: nobody is tagged to a booth in his/her home or posting block. When both officer and booth have a block code (e.g. census code), the code decides.</v>
+        <v>PIN                 — unique. Leave blank to auto-generate (district code + serial).</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>Officers — Office Code (or Office Name if no code) is used for the rule that the 4 members of a party must be from different offices. Codes protect against spelling mistakes in names.</v>
+        <v>Name, Designation   — as printed on letters.</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v/>
+        <v>Office Code         — recommended. Same code = same office (spelling of Office Name then does not matter). Used for: 4 party members from 4 different offices.</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>Leave PIN blank to auto-generate it (district code + serial). Delete the two example rows before use.</v>
+        <v>Office Name / Address, Mobile — printed on letters and registers. Mobile 10 digits.</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="str">
+        <v>Duty                — PRESIDING OFFICER, POLLING OFFICER-1, POLLING OFFICER-2, POLLING OFFICER-3, PATROLLING MAGISTRATE, MICRO OBSERVER</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="str">
+        <v xml:space="preserve">                      (short forms PrO, P1, P2, P3, PCCP, MO also accepted).</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="str">
+        <v>Home Block Code / Home Block       — block where the officer lives.</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="str">
+        <v>Posting Block Code / Posting Block — block where the officer works.</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="str">
+        <v xml:space="preserve">                      Nobody is tagged to a booth in his/her home or posting block. When the officer and the booth both have a block code (e.g. 2011 census code), the code decides.</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="str">
+        <v xml:space="preserve">                      Name or code is enough; both are better. Leading zeros may be lost in Excel (0101 → 101) — this does not matter.</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="str">
+        <v>OUT OF DISTRICT     — if the home or posting block is outside the district, write code 999999 (or name "Others").</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="str">
+        <v xml:space="preserve">                      Such a block excludes no booth (the officer can go to any block except an in-district one he/she belongs to).</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="str">
+        <v>Account No, Bank, Branch, IFSC — optional; printed on training attendance sheets.</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:A6"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:A15"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/test-data/Officers_Template.xlsx
+++ b/test-data/Officers_Template.xlsx
@@ -398,7 +398,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:P4"/>
+  <dimension ref="A1:Q4"/>
   <cols>
     <col min="1" max="1" width="12.83203125" customWidth="1"/>
     <col min="2" max="2" width="24.83203125" customWidth="1"/>
@@ -416,6 +416,7 @@
     <col min="14" max="14" width="14.83203125" customWidth="1"/>
     <col min="15" max="15" width="14.83203125" customWidth="1"/>
     <col min="16" max="16" width="13.83203125" customWidth="1"/>
+    <col min="17" max="17" width="11.83203125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -467,6 +468,9 @@
       <c r="P1" t="str">
         <v>IFSC</v>
       </c>
+      <c r="Q1" t="str">
+        <v>Blood Group</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="str">
@@ -517,6 +521,9 @@
       <c r="P2" t="str">
         <v>SBIN0000001</v>
       </c>
+      <c r="Q2" t="str">
+        <v>B+</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
@@ -620,14 +627,14 @@
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:P4"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:Q4"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:A15"/>
+  <dimension ref="A1:A16"/>
   <cols>
     <col min="1" max="1" width="120.83203125" customWidth="1"/>
   </cols>
@@ -707,9 +714,14 @@
         <v>Account No, Bank, Branch, IFSC — optional; printed on training attendance sheets.</v>
       </c>
     </row>
+    <row r="16">
+      <c r="A16" t="str">
+        <v>Blood Group — optional; printed on the identity card when filled.</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:A15"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:A16"/>
   </ignoredErrors>
 </worksheet>
 </file>